--- a/project/output/csv/main/analysis_results/statistical_results.xlsx
+++ b/project/output/csv/main/analysis_results/statistical_results.xlsx
@@ -461,7 +461,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-01-21 11:49:43</t>
+          <t>2026-02-03 23:46:34</t>
         </is>
       </c>
     </row>

--- a/project/output/csv/main/analysis_results/statistical_results.xlsx
+++ b/project/output/csv/main/analysis_results/statistical_results.xlsx
@@ -461,7 +461,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-02-03 23:46:34</t>
+          <t>2026-02-04 09:58:19</t>
         </is>
       </c>
     </row>

--- a/project/output/csv/main/analysis_results/statistical_results.xlsx
+++ b/project/output/csv/main/analysis_results/statistical_results.xlsx
@@ -461,7 +461,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-02-04 09:58:19</t>
+          <t>2026-02-04 11:57:53</t>
         </is>
       </c>
     </row>
@@ -473,7 +473,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>/Users/toshiki/Desktop/dev/midAir_display_image/project/output/csv/main</t>
+          <t>/Users/toshiki/Desktop/dev/midAir_display_image/project/output/csv/main/../../../output/csv/main</t>
         </is>
       </c>
     </row>

--- a/project/output/csv/main/analysis_results/statistical_results.xlsx
+++ b/project/output/csv/main/analysis_results/statistical_results.xlsx
@@ -461,7 +461,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-02-04 11:57:53</t>
+          <t>2026-02-09 18:53:54</t>
         </is>
       </c>
     </row>
@@ -473,7 +473,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>/Users/toshiki/Desktop/dev/midAir_display_image/project/output/csv/main/../../../output/csv/main</t>
+          <t>/Users/toshiki/Desktop/dev/midAir_display_image/project/output/csv/main</t>
         </is>
       </c>
     </row>
